--- a/data/trans_bre/IP16A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,33; 6,42</t>
+          <t>-12,27; 6,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,48; -2,02</t>
+          <t>-19,96; -2,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 0,0</t>
+          <t>-13,78; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 0,0</t>
+          <t>-20,55; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 14,88</t>
+          <t>-2,44; 15,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 5,52</t>
+          <t>-3,4; 5,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 0,0</t>
+          <t>-11,06; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 4,68</t>
+          <t>-7,55; 4,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,29; 998,77</t>
+          <t>-51,1; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 4,58</t>
+          <t>-15,13; 3,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 17,36</t>
+          <t>-3,37; 17,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 9,45</t>
+          <t>-9,48; 9,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 4,07</t>
+          <t>-5,33; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 399,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,89; —</t>
+          <t>-61,16; 998,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 1,35</t>
+          <t>-20,07; 0,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 10,44</t>
+          <t>-2,35; 10,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 0,24</t>
+          <t>-18,39; 1,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 7,31</t>
+          <t>-7,6; 6,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 161,45</t>
+          <t>-100,0; 244,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 3,48</t>
+          <t>-6,72; 3,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,16</t>
+          <t>-3,16; 4,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,58; -0,13</t>
+          <t>-7,35; 0,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 1,0</t>
+          <t>-4,75; 0,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-63,51; 80,24</t>
+          <t>-67,23; 72,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 200,84</t>
+          <t>-57,44; 217,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-93,5; 26,01</t>
+          <t>-93,38; 17,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-90,6; 82,78</t>
+          <t>-89,86; 79,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 6,26</t>
+          <t>-11,08; 6,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,96; -2,0</t>
+          <t>-22,06; -1,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 0,0</t>
+          <t>-13,98; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 0,0</t>
+          <t>-20,69; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 15,91</t>
+          <t>-3,25; 14,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 5,51</t>
+          <t>-4,88; 5,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,06; 0,0</t>
+          <t>-12,61; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 4,49</t>
+          <t>-6,9; 5,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,1; —</t>
+          <t>-57,88; 967,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 3,93</t>
+          <t>-13,85; 4,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 17,09</t>
+          <t>-3,22; 17,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 9,52</t>
+          <t>-10,75; 9,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 3,29</t>
+          <t>-4,65; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-61,16; 998,87</t>
+          <t>-58,66; 1006,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 0,85</t>
+          <t>-18,9; 0,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 10,46</t>
+          <t>-3,75; 10,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 1,95</t>
+          <t>-17,74; 0,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 6,42</t>
+          <t>-7,61; 6,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 244,33</t>
+          <t>-100,0; 336,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 3,13</t>
+          <t>-6,21; 3,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 4,18</t>
+          <t>-3,28; 4,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,02</t>
+          <t>-7,17; -0,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,68</t>
+          <t>-4,67; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,23; 72,66</t>
+          <t>-61,79; 72,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-57,44; 217,49</t>
+          <t>-56,74; 230,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-93,38; 17,24</t>
+          <t>-93,36; 29,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-89,86; 79,94</t>
+          <t>-90,07; 104,97</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>-1,59</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 6,37</t>
+          <t>-11,33; 6,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,06; -1,99</t>
+          <t>-22,48; -2,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 0,0</t>
+          <t>-14,61; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,69; 0,0</t>
+          <t>-10,07; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,34</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-52,38%</t>
+          <t>-62,54%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 14,89</t>
+          <t>-2,31; 14,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 5,49</t>
+          <t>-3,49; 5,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 0,0</t>
+          <t>-11,9; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 5,53</t>
+          <t>-9,05; 2,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,88; 967,16</t>
+          <t>-60,29; 998,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 4,26</t>
+          <t>-13,86; 4,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 17,25</t>
+          <t>-4,4; 17,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 9,75</t>
+          <t>-9,67; 9,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,4</t>
+          <t>-4,49; 5,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 399,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 1006,96</t>
+          <t>-62,89; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-31,9%</t>
+          <t>-31,03%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,9; 0,62</t>
+          <t>-19,42; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 10,34</t>
+          <t>-2,34; 10,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 0,07</t>
+          <t>-17,73; 0,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 6,11</t>
+          <t>-7,53; 7,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 336,22</t>
+          <t>-100,0; 161,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-1,32</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-51,17%</t>
+          <t>-42,14%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 3,26</t>
+          <t>-6,47; 3,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,22</t>
+          <t>-3,38; 4,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -0,04</t>
+          <t>-7,58; -0,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,37</t>
+          <t>-4,62; 1,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 72,27</t>
+          <t>-63,51; 80,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-56,74; 230,64</t>
+          <t>-59,61; 200,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-93,36; 29,08</t>
+          <t>-93,5; 26,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-90,07; 104,97</t>
+          <t>-88,42; 133,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A03-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP16A03-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,169 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-7,57</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,8</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,59</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-16,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.0498935534746248</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.684370748496777</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.4570608975775851</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.3110388450137094</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.05411523781558002</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-11,33; 6,42</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-22,48; -2,02</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-14,61; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-10,07; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.709654407021171</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.736243916856786</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.283686606265352</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-1.69635312496525</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.926164392019187</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-0.4337120824539979</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,43</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>119,06%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-62,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,31; 14,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,49; 5,52</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,9; 0,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-9,05; 2,91</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-60,29; 998,77</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.273060295038418</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.06109601942443314</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.6284250343567359</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.7877098738746946</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1.400859798987904</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.2025002946678966</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.6923909723508627</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-4,11</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,83</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,74</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,59</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-51,34%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>110,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>34,1%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.274862150991997</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.6039585092475857</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.36098849025647</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.311806958052066</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3967207207847074</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-13,86; 4,58</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-4,4; 17,36</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-9,67; 9,45</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-4,49; 5,63</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 399,46</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-62,89; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.270944922121175</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.446443083126869</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.306063042248155</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +789,271 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-8,43</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3,28</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,62</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-75,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>174,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-75,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-31,03%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.168607184816094</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.212331096230521</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1860128266837428</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.2213225701031261</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.621415072839908</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.057858880795334</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.2095863040113818</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.4108468608428208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-19,42; 1,35</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,34; 10,44</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-17,73; 0,24</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,53; 7,53</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 161,45</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.731934669170037</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.8290748985759399</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.87727735346887</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.366277549977388</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="n">
+        <v>-0.6548450675027063</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.3829043068758269</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.999935639449122</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1.767279072561359</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1.697333131941985</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.745841976614757</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5953308336066508</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.9449185870385182</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.2372166909969123</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.8416291752271813</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1.389324814138302</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.7353313900062106</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3409202014267072</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.949321401536844</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-0.8451940410892999</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.80692667487028</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.416324148411999</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>-0.2816075880298559</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.171641734665175</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.3507522337851695</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.053451913717666</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>1.005663157556596</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,47</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-20,15%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,05%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-62,93%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-42,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-6,47; 3,48</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 4,16</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-7,58; -0,13</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,62; 1,44</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-63,51; 80,24</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-59,61; 200,84</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-93,5; 26,01</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-88,42; 133,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.3797130717438436</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.1156082024379121</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.4957886021182859</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.3253107828305601</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2622341975988504</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1431207508841174</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.5946864788720646</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.4407119097468404</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.388251640322975</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.7136121718337404</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.132153178435306</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.049923695919721</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.6798991359455829</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.6228170775903877</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.9107462189744483</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.8822653519265535</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.498076000158737</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8733554020655726</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1955701114335468</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.2949114485462545</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.6154082821835989</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>2.244339145483051</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.047053348585441</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.122747454563834</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1061,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
